--- a/publication_tables/supplementary/S13_negative_income_diagnostic.xlsx
+++ b/publication_tables/supplementary/S13_negative_income_diagnostic.xlsx
@@ -484,22 +484,22 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00618560749563</v>
+        <v>0.006185607495628549</v>
       </c>
       <c r="E2" t="n">
-        <v>-14.263052618</v>
+        <v>-32.44243587034595</v>
       </c>
       <c r="F2" t="n">
-        <v>154980.713684</v>
+        <v>154980.7136842105</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8738371728</v>
+        <v>7.875287483341486</v>
       </c>
       <c r="H2" t="n">
-        <v>7.87383660353</v>
+        <v>7.875286188495376</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.69268543416e-07</v>
+        <v>-1.294846110333481e-06</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>One row per flagged unsupported-shock configuration. The current output contains energy_only / shock.</t>
+          <t>One row per configuration with negative reconstructed household income. An empty Data sheet means no configuration was flagged; see income_boundary_check.json for the complete audit.</t>
         </is>
       </c>
     </row>
